--- a/artfynd/A 57979-2025 artfynd.xlsx
+++ b/artfynd/A 57979-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128758656</v>
+        <v>128297653</v>
       </c>
       <c r="B2" t="n">
-        <v>88727</v>
+        <v>88954</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4377</v>
+        <v>360</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodvaxing</t>
+          <t>Vridfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Clavaria amoenoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Corner &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -713,19 +713,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Håvberget, Håvberget, Dlr</t>
+          <t>Håvberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479016</v>
+        <v>478952</v>
       </c>
       <c r="R2" t="n">
-        <v>6682528</v>
+        <v>6682544</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca.</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +775,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +787,1810 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>67891939</v>
+      </c>
+      <c r="B3" t="n">
+        <v>89066</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>803</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lutvaxing</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neohygrocybe nitrata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.) Kovalenko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Håvberget "G:a åkern", Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>479015</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6682503</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Restaurering pågår.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128301424</v>
+      </c>
+      <c r="B4" t="n">
+        <v>89066</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>803</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lutvaxing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neohygrocybe nitrata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Kovalenko</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Håvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478952</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6682544</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128299526</v>
+      </c>
+      <c r="B5" t="n">
+        <v>88980</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hagfingersvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Clavulinopsis helvola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pers.) Corner</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Håvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478952</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6682544</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128299488</v>
+      </c>
+      <c r="B6" t="n">
+        <v>89081</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4374</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulvaxing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Håvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478952</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6682544</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>67891932</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Håvberget "G:a åkern", Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>479015</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6682503</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca. Senast 2011. Restaurering pågår.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103858377</v>
+      </c>
+      <c r="B8" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Håvberget 22, Vansbro, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>479019</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6682523</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>103865702</v>
+      </c>
+      <c r="B9" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Håvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>478952</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6682544</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128758656</v>
+      </c>
+      <c r="B10" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Håvberget, Håvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>479016</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6682528</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128299583</v>
+      </c>
+      <c r="B11" t="n">
+        <v>89029</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4392</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ängsvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Håvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>478952</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6682544</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>103865707</v>
+      </c>
+      <c r="B12" t="n">
+        <v>89106</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4394</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Honungsvaxing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hygrocybe reidii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Håvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478952</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6682544</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111916594</v>
+      </c>
+      <c r="B13" t="n">
+        <v>89035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4398</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Håvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>478933</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6682568</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Kjell-Åke Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>86406372</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Håvberget "G:a åkern", Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>479015</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6682503</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-06-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>101850896</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Håvberget 19:1, Vansbro, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>479012</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6682503</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126767565</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Håvberget "G:a åkern", Håvberget "G:a åkern", Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>479033</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6682497</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128298931</v>
+      </c>
+      <c r="B17" t="n">
+        <v>89079</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Håvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478952</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6682544</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128758733</v>
+      </c>
+      <c r="B18" t="n">
+        <v>89079</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Håvberget, Håvberget "G:a åkern", Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>479027</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6682508</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57979-2025 artfynd.xlsx
+++ b/artfynd/A 57979-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128297653</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67891939</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128301424</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128299526</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128299488</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67891932</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103858377</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103865702</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1698,6 +1743,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758656</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1810,6 +1860,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128299583</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1911,6 +1966,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103865707</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111916594</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2126,6 +2191,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86406372</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2248,6 +2318,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101850896</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2368,6 +2443,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126767565</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2489,6 +2569,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135088307</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2596,6 +2681,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128298931</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2712,8 +2802,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758733</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 57979-2025 artfynd.xlsx
+++ b/artfynd/A 57979-2025 artfynd.xlsx
@@ -2454,7 +2454,7 @@
         <v>135088307</v>
       </c>
       <c r="B17" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 57979-2025 artfynd.xlsx
+++ b/artfynd/A 57979-2025 artfynd.xlsx
@@ -2454,7 +2454,7 @@
         <v>135088307</v>
       </c>
       <c r="B17" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
